--- a/workbooks/11 Formulas 7 - Dynamic Arrays.xlsx
+++ b/workbooks/11 Formulas 7 - Dynamic Arrays.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="693">
   <si>
     <t>Challenge</t>
   </si>
@@ -1149,46 +1149,49 @@
     <t>Multiply.</t>
   </si>
   <si>
+    <t>Which move is this? Multiply conditions for AND; add them for OR.</t>
+  </si>
+  <si>
+    <t>F7-2 Sifter T3</t>
+  </si>
+  <si>
+    <t>After array and include.</t>
+  </si>
+  <si>
+    <t>Which FILTER argument number sets what to show when nothing matches?</t>
+  </si>
+  <si>
+    <t>▶ Open F7-2 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F7-2 Sifter C1</t>
+  </si>
+  <si>
+    <t>=FILTER</t>
+  </si>
+  <si>
+    <t>=FILTER(</t>
+  </si>
+  <si>
+    <t>=FILTER()</t>
+  </si>
+  <si>
+    <t>FILTER(</t>
+  </si>
+  <si>
+    <t>FILTER()</t>
+  </si>
+  <si>
+    <t>F7-2 Sifter C2</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>ASTERISK</t>
+  </si>
+  <si>
     <t>In FILTER, which operator joins two conditions so BOTH must be true?</t>
-  </si>
-  <si>
-    <t>F7-2 Sifter T3</t>
-  </si>
-  <si>
-    <t>After array and include.</t>
-  </si>
-  <si>
-    <t>Which FILTER argument number sets what to show when nothing matches?</t>
-  </si>
-  <si>
-    <t>▶ Open F7-2 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F7-2 Sifter C1</t>
-  </si>
-  <si>
-    <t>=FILTER</t>
-  </si>
-  <si>
-    <t>=FILTER(</t>
-  </si>
-  <si>
-    <t>=FILTER()</t>
-  </si>
-  <si>
-    <t>FILTER(</t>
-  </si>
-  <si>
-    <t>FILTER()</t>
-  </si>
-  <si>
-    <t>F7-2 Sifter C2</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>ASTERISK</t>
   </si>
   <si>
     <t>F7-2 Sifter C3</t>
@@ -2014,31 +2017,34 @@
     <t>The inner one.</t>
   </si>
   <si>
+    <t>Which move is this? Nest dynamic functions: the inner result feeds the outer one.</t>
+  </si>
+  <si>
+    <t>▶ Open F7-4 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F7-4 Combo C1</t>
+  </si>
+  <si>
+    <t>=LET</t>
+  </si>
+  <si>
+    <t>=LET(</t>
+  </si>
+  <si>
+    <t>=LET()</t>
+  </si>
+  <si>
+    <t>LET(</t>
+  </si>
+  <si>
+    <t>LET()</t>
+  </si>
+  <si>
+    <t>F7-4 Combo C2</t>
+  </si>
+  <si>
     <t>In =SORT(UNIQUE(E6:E25)), which function removes the duplicates?</t>
-  </si>
-  <si>
-    <t>▶ Open F7-4 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F7-4 Combo C1</t>
-  </si>
-  <si>
-    <t>=LET</t>
-  </si>
-  <si>
-    <t>=LET(</t>
-  </si>
-  <si>
-    <t>=LET()</t>
-  </si>
-  <si>
-    <t>LET(</t>
-  </si>
-  <si>
-    <t>LET()</t>
-  </si>
-  <si>
-    <t>F7-4 Combo C2</t>
   </si>
   <si>
     <t>F7-4 Combo C3</t>
@@ -3202,7 +3208,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3212,12 +3218,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3227,32 +3233,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3262,30 +3268,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F7-1 Spill Zone'!$G$14:$G$41)&amp;" / 210"</f>
@@ -3300,15 +3306,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F7-2 Sifter'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3323,15 +3329,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F7-3 Sorter'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3346,15 +3352,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F7-4 Combo'!$G$12:$G$36)&amp;" / 180"</f>
@@ -3369,15 +3375,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM(Boss!$G$14:$G$35)&amp;" / 180"</f>
@@ -3392,12 +3398,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">(SUM('F7-1 Spill Zone'!$G$14:$G$41)+SUM('F7-2 Sifter'!$G$13:$G$38)+SUM('F7-3 Sorter'!$G$13:$G$39)+SUM('F7-4 Combo'!$G$12:$G$36)+SUM(Boss!$G$14:$G$35))&amp;" / 960"</f>
@@ -3406,19 +3412,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">_xlfn.LET(_xlpm.p,(SUM('F7-1 Spill Zone'!$G$14:$G$41)+SUM('F7-2 Sifter'!$G$13:$G$38)+SUM('F7-3 Sorter'!$G$13:$G$39)+SUM('F7-4 Combo'!$G$12:$G$36)+SUM(Boss!$G$14:$G$35))/960,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3427,7 +3433,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3436,7 +3442,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>
@@ -3473,7 +3479,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3484,7 +3490,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3503,7 +3509,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3514,19 +3520,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C8" s="31" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -3535,7 +3541,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C9" s="31">
         <v>15</v>
@@ -3543,7 +3549,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F7-1 Spill Zone'!$G$14:$G$41)&gt;=210*0.5,SUM('F7-2 Sifter'!$G$13:$G$38)&gt;=190*0.5,SUM('F7-3 Sorter'!$G$13:$G$39)&gt;=200*0.5,SUM('F7-4 Combo'!$G$12:$G$36)&gt;=180*0.5),"OPEN","LOCKED")</f>
@@ -3556,7 +3562,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3590,7 +3596,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B14" s="32" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function lets you name a value inside a formula?  (from F7-4 Combo)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3613,7 +3619,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B15" s="32" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","In =SORT"&amp;"(UNIQUE"&amp;"(E6:E25)), which function removes the duplicates?  (from F7-4 Combo)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3636,7 +3642,7 @@
     </row>
     <row r="16" spans="1:7" ht="51.25" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B16" s="32" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","What is it called when one formula's results flow into neighboring cells?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3659,7 +3665,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B17" s="32" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which error appears when a spill range is blocked?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3682,7 +3688,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B18" s="32" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","How do you refer to the whole spill that starts in H5?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3705,7 +3711,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B19" s="32" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which function spills a list of sequential numbers?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3728,7 +3734,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which function returns only the rows that meet a condition?  (from F7-2 Sifter)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3751,7 +3757,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","In FILTER, which operator joins two conditions so BOTH must be true?  (from F7-2 Sifter)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3774,7 +3780,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3785,7 +3791,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3813,14 +3819,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In K6 spill the numbers 1 to 5.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$K$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2801)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$K$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2801)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$K$6)=_xlfn.ANCHORARRAY(Key!$E$2801)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2801))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2801))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SEQUENCE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SEQUENCE"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3838,14 +3844,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In M6 spill the West orders, every column.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$M$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2901)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$M$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2901)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$M$6)=_xlfn.ANCHORARRAY(Key!$E$2901)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2901))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2901))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3863,14 +3869,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In K14 spill the Order IDs of Kim's orders with more than 20 units.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$K$14),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$K$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$K$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$K$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$K$14))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3001)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$K$14))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3001)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$K$14)=_xlfn.ANCHORARRAY(Key!$E$3001)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3001))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3001))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$14)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3888,14 +3894,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In K30 spill the Units column sorted largest first.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$K$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$K$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$K$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$K$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$K$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3101)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$K$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3101)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$K$30)=_xlfn.ANCHORARRAY(Key!$E$3101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$30)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3913,14 +3919,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In M30 spill each Product once.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$M$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3201)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$M$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3201)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$M$30)=_xlfn.ANCHORARRAY(Key!$E$3201)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3201))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3201))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$30)))))),"✔ CLEAR","✘ CLOSE · right result, but use UNIQUE"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3938,14 +3944,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In O30 count the different Products.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$O$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$O$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$O$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$O$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$O$30),ABS('Boss Arena'!$O$30-Key!$C$93)&lt;=1E-9*MAX(1,ABS(Key!$C$93))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTA"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$O$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$O$30)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTA and UNIQUE"))))),"LOCKED")</f>
@@ -3963,14 +3969,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In Q30 spill each Rep once, sorted A→Z.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$Q$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$Q$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$Q$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$Q$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3301)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3301)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30)=_xlfn.ANCHORARRAY(Key!$E$3301)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3301))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3301))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$Q$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$Q$30)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT and UNIQUE"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3988,14 +3994,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In U13 add up the whole spill in U6 with U6#.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$U$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$U$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$U$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$U$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$U$13),ABS('Boss Arena'!$U$13-Key!$C$95)&lt;=1E-9*MAX(1,ABS(Key!$C$95))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("#",_xlfn.FORMULATEXT('Boss Arena'!$U$13))),"✔ CLEAR","✘ CLOSE · your formula needs #"))))),"LOCKED")</f>
@@ -4013,14 +4019,14 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B34" s="32" cm="1" t="str">
         <f t="array" ref="B34">IF($C$10="OPEN","In W6 spill the Order IDs sorted by Date, newest first, with SORTBY.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$W$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$W$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$W$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$W$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$W$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3401)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$W$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3401)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$W$6)=_xlfn.ANCHORARRAY(Key!$E$3401)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3401))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3401))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORTBY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$W$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORTBY"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -4038,14 +4044,14 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B35" s="32" cm="1" t="str">
         <f t="array" ref="B35">IF($C$10="OPEN","In W30 filter the Order IDs for the region ""Central"" and show None when nothing matches.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D35" s="21" cm="1" t="str">
         <f t="array" ref="D35">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$W$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$W$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$W$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$W$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$W$30),'Boss Arena'!$W$30=Key!$C$97),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$W$30)))))),"✔ CLEAR","✘ CLOSE · right value, but use FILTER"))))),"LOCKED")</f>
@@ -4171,7 +4177,7 @@
   <sheetData>
     <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -4184,10 +4190,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -4213,16 +4219,16 @@
         <v>15</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="U5" s="27" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="W5" s="27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -4393,7 +4399,7 @@
         <v>1500</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -4419,7 +4425,7 @@
         <v>2250</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="U13" s="29"/>
     </row>
@@ -4702,19 +4708,19 @@
     </row>
     <row r="29" spans="2:23">
       <c r="K29" s="27" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M29" s="27" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O29" s="27" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="Q29" s="27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="W29" s="27" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" spans="2:23">
@@ -4749,7 +4755,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4757,189 +4763,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>61</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>64</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>184</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>169</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>168</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>285</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>284</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>185</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>183</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>174</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -5703,7 +5709,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s">
         <v>291</v>
@@ -5712,37 +5718,37 @@
         <v>62</v>
       </c>
       <c r="F38" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G38" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C41" cm="1" t="str">
         <f t="array" ref="C41">_xlfn._xlws.FILTER('F7-2 Arena'!$B$6:$B$25,'F7-2 Arena'!$D$6:$D$25="Central","None")</f>
@@ -5751,7 +5757,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s">
         <v>283</v>
@@ -5777,7 +5783,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s">
         <v>288</v>
@@ -5791,7 +5797,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s">
         <v>291</v>
@@ -5800,200 +5806,200 @@
         <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E45" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F45" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G45" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H45" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I45" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J45" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E46" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F46" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G46" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H46" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I46" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J46" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E47" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F47" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G47" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H47" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I47" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J47" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E48" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F48" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G48" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H48" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I48" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J48" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E49" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F49" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G49" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H49" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I49" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J49" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E50" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F50" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G50" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H50" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I50" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J50" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E51" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F51" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G51" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H51" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I51" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J51" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s">
         <v>95</v>
@@ -6016,10 +6022,10 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" t="s">
         <v>284</v>
@@ -6039,10 +6045,10 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C54" t="s">
         <v>185</v>
@@ -6062,112 +6068,112 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s">
         <v>95</v>
       </c>
       <c r="E55" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F55" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G55" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H55" t="s">
         <v>285</v>
       </c>
       <c r="I55" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J55" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E56" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F56" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G56" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H56" t="s">
         <v>284</v>
       </c>
       <c r="I56" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J56" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E57" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F57" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G57" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H57" t="s">
         <v>185</v>
       </c>
       <c r="I57" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J57" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C61" cm="1">
         <f t="array" ref="C61">COUNTA(_xlfn.UNIQUE('F7-3 Arena'!$E$6:$E$25))</f>
@@ -6176,258 +6182,258 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B62" t="s">
         <v>95</v>
       </c>
       <c r="E62" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F62" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G62" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H62" t="s">
         <v>285</v>
       </c>
       <c r="I62" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J62" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B63" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E63" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F63" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G63" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H63" t="s">
         <v>284</v>
       </c>
       <c r="I63" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J63" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B64" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E64" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F64" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G64" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H64" t="s">
         <v>185</v>
       </c>
       <c r="I64" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J64" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E65" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F65" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G65" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H65" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I65" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J65" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B66" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E66" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F66" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E67" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F67" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G67" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H67" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I67" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J67" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B68" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E68" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F68" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G68" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H68" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I68" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J68" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B69" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E69" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F69" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G69" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H69" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I69" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J69" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E70" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F70" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G70" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H70" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I70" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J70" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B71" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E71" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F71" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G71" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H71" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I71" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J71" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C72" t="s">
         <v>183</v>
@@ -6447,10 +6453,10 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B73" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C73" t="s">
         <v>174</v>
@@ -6470,36 +6476,36 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B74" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E74" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F74" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G74" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H74" t="s">
         <v>183</v>
       </c>
       <c r="I74" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J74" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B75" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E75" t="s">
         <v>185</v>
@@ -6507,10 +6513,10 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B76" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C76" cm="1">
         <f t="array" ref="C76">AVERAGE('F7-4 Arena'!$H$6:$H$25)</f>
@@ -6519,23 +6525,23 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B77" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B78" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B79" t="s">
         <v>218</v>
@@ -6547,36 +6553,36 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B80" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E80" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F80" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G80" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H80" t="s">
         <v>183</v>
       </c>
       <c r="I80" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J80" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B81" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E81" t="s">
         <v>185</v>
@@ -6584,7 +6590,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B82" t="s">
         <v>167</v>
@@ -6601,7 +6607,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B83" t="s">
         <v>173</v>
@@ -6618,7 +6624,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B84" t="s">
         <v>178</v>
@@ -6629,7 +6635,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B85" t="s">
         <v>182</v>
@@ -6655,7 +6661,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B86" t="s">
         <v>283</v>
@@ -6681,7 +6687,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B87" t="s">
         <v>288</v>
@@ -6695,50 +6701,50 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B88" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B89" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B90" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B91" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B92" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B93" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C93" cm="1">
         <f t="array" ref="C93">COUNTA(_xlfn.UNIQUE('Boss Arena'!$F$6:$F$25))</f>
@@ -6747,18 +6753,18 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B94" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B95" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C95" cm="1">
         <f t="array" ref="C95">SUM(_xlfn.ANCHORARRAY('Boss Arena'!$U$6))</f>
@@ -6767,18 +6773,18 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B96" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B97" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C97" cm="1" t="str">
         <f t="array" ref="C97">_xlfn._xlws.FILTER('Boss Arena'!$B$6:$B$25,'Boss Arena'!$D$6:$D$25="Central","None")</f>
@@ -8260,7 +8266,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8271,7 +8277,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8771,7 +8777,7 @@
         <v>197</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -8815,10 +8821,10 @@
         <v>206</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F7-2 Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('F7-2 Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-2 Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-2 Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101)),COLUMNS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101)),SUM(--(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$6)=_xlfn.ANCHORARRAY(Key!$E$2101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-2 Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN"))))</f>
@@ -8839,10 +8845,10 @@
         <v>209</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F7-2 Arena'!$K$20),"",IF(NOT(_xlfn.ISFORMULA('F7-2 Arena'!$K$20)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-2 Arena'!$K$20),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-2 Arena'!$K$20),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$20))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2201)),COLUMNS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$20))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2201)),SUM(--(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$20)=_xlfn.ANCHORARRAY(Key!$E$2201)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2201))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2201))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-2 Arena'!$K$20)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN"))))</f>
@@ -8863,10 +8869,10 @@
         <v>214</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F7-2 Arena'!$K$30),"",IF(NOT(_xlfn.ISFORMULA('F7-2 Arena'!$K$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-2 Arena'!$K$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-2 Arena'!$K$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F7-2 Arena'!$K$30),'F7-2 Arena'!$K$30=Key!$C$41),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-2 Arena'!$K$30)))))),"✔ CLEAR","✘ CLOSE · right value, but use FILTER")))))</f>
@@ -9546,7 +9552,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9557,7 +9563,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9609,7 +9615,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>285</v>
@@ -9620,7 +9626,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>284</v>
@@ -9631,7 +9637,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>185</v>
@@ -9676,7 +9682,7 @@
         <v>82</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9698,7 +9704,7 @@
         <v>92</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9720,7 +9726,7 @@
         <v>102</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -9742,7 +9748,7 @@
         <v>111</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9764,7 +9770,7 @@
         <v>120</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9786,7 +9792,7 @@
         <v>129</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9808,7 +9814,7 @@
         <v>139</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9830,7 +9836,7 @@
         <v>149</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9852,7 +9858,7 @@
         <v>159</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9874,7 +9880,7 @@
         <v>163</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -9930,7 +9936,7 @@
         <v>170</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -9952,7 +9958,7 @@
         <v>175</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -9974,7 +9980,7 @@
         <v>179</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -10004,7 +10010,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -10035,7 +10041,7 @@
         <v>194</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -10057,7 +10063,7 @@
         <v>197</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -10079,7 +10085,7 @@
         <v>199</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10101,10 +10107,10 @@
         <v>206</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F7-3 Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-3 Arena'!$K$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2301)),COLUMNS(_xlfn.ANCHORARRAY('F7-3 Arena'!$K$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2301)),SUM(--(_xlfn.ANCHORARRAY('F7-3 Arena'!$K$6)=_xlfn.ANCHORARRAY(Key!$E$2301)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2301))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2301))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT"),"✘ TRY AGAIN"))))</f>
@@ -10125,10 +10131,10 @@
         <v>209</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F7-3 Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-3 Arena'!$M$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2401)),COLUMNS(_xlfn.ANCHORARRAY('F7-3 Arena'!$M$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2401)),SUM(--(_xlfn.ANCHORARRAY('F7-3 Arena'!$M$6)=_xlfn.ANCHORARRAY(Key!$E$2401)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2401))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2401))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORTBY"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORTBY"),"✘ TRY AGAIN"))))</f>
@@ -10149,10 +10155,10 @@
         <v>214</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F7-3 Arena'!$O$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$O$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$O$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$O$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-3 Arena'!$O$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2501)),COLUMNS(_xlfn.ANCHORARRAY('F7-3 Arena'!$O$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2501)),SUM(--(_xlfn.ANCHORARRAY('F7-3 Arena'!$O$6)=_xlfn.ANCHORARRAY(Key!$E$2501)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2501))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2501))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$O$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use UNIQUE"),"✘ TRY AGAIN"))))</f>
@@ -10173,10 +10179,10 @@
         <v>219</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F7-3 Arena'!$Q$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$Q$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$Q$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$Q$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F7-3 Arena'!$Q$6),ABS('F7-3 Arena'!$Q$6-Key!$C$61)&lt;=1E-9*MAX(1,ABS(Key!$C$61))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTA"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$Q$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$Q$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTA and UNIQUE")))))</f>
@@ -10314,7 +10320,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -10327,10 +10333,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -10356,16 +10362,16 @@
         <v>15</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O5" s="27" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -10860,7 +10866,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10871,7 +10877,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10923,7 +10929,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>183</v>
@@ -10934,7 +10940,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>174</v>
@@ -10979,7 +10985,7 @@
         <v>82</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" cm="1" t="str">
@@ -11001,7 +11007,7 @@
         <v>92</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -11023,7 +11029,7 @@
         <v>102</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -11045,7 +11051,7 @@
         <v>111</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -11067,7 +11073,7 @@
         <v>120</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -11089,7 +11095,7 @@
         <v>129</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -11111,7 +11117,7 @@
         <v>139</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -11133,7 +11139,7 @@
         <v>149</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -11155,7 +11161,7 @@
         <v>159</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -11177,7 +11183,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -11233,7 +11239,7 @@
         <v>170</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -11255,7 +11261,7 @@
         <v>175</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -11285,7 +11291,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -11316,7 +11322,7 @@
         <v>194</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -11338,7 +11344,7 @@
         <v>197</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -11360,10 +11366,10 @@
         <v>199</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F7-4 Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F7-4 Arena'!$K$6),ABS('F7-4 Arena'!$K$6-Key!$C$76)&lt;=1E-9*MAX(1,ABS(Key!$C$76))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LET"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use LET")))))</f>
@@ -11384,10 +11390,10 @@
         <v>206</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(ISBLANK('F7-4 Arena'!$K$10),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$10))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2601)),COLUMNS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$10))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2601)),SUM(--(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$10)=_xlfn.ANCHORARRAY(Key!$E$2601)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2601))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2601))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$10))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$10)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT and UNIQUE"),"✘ TRY AGAIN"))))</f>
@@ -11408,10 +11414,10 @@
         <v>209</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D35" s="21" cm="1" t="str">
         <f t="array" ref="D35">IF(ISBLANK('F7-4 Arena'!$K$20),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$20)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$20),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$20),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$20))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2701)),COLUMNS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$20))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2701)),SUM(--(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$20)=_xlfn.ANCHORARRAY(Key!$E$2701)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2701))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2701))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$20))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$20))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$20)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT and UNIQUE and FILTER"),"✘ TRY AGAIN"))))</f>
@@ -11432,10 +11438,10 @@
         <v>214</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F7-4 Arena'!$K$30),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F7-4 Arena'!$K$30),ABS('F7-4 Arena'!$K$30-Key!$C$79)&lt;=1E-9*MAX(1,ABS(Key!$C$79))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("#",_xlfn.FORMULATEXT('F7-4 Arena'!$K$30))),"✔ CLEAR","✘ CLOSE · your formula needs #")))))</f>
@@ -11563,7 +11569,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -11576,10 +11582,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -11605,10 +11611,10 @@
         <v>15</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -11708,7 +11714,7 @@
         <v>1000</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -11942,7 +11948,7 @@
         <v>1200</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -12086,7 +12092,7 @@
     </row>
     <row r="29" spans="2:11">
       <c r="K29" s="27" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="30" spans="2:11">

--- a/workbooks/11 Formulas 7 - Dynamic Arrays.xlsx
+++ b/workbooks/11 Formulas 7 - Dynamic Arrays.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="698">
   <si>
     <t>Challenge</t>
   </si>
@@ -675,6 +675,24 @@
     <t>The position finder.</t>
   </si>
   <si>
+    <t>=XMATCH</t>
+  </si>
+  <si>
+    <t>=XMATCH(</t>
+  </si>
+  <si>
+    <t>=XMATCH()</t>
+  </si>
+  <si>
+    <t>XMATCH</t>
+  </si>
+  <si>
+    <t>XMATCH(</t>
+  </si>
+  <si>
+    <t>XMATCH()</t>
+  </si>
+  <si>
     <t>W10</t>
   </si>
   <si>
@@ -775,6 +793,21 @@
   </si>
   <si>
     <t>#SPILL</t>
+  </si>
+  <si>
+    <t>=SPILL</t>
+  </si>
+  <si>
+    <t>=SPILL(</t>
+  </si>
+  <si>
+    <t>=SPILL()</t>
+  </si>
+  <si>
+    <t>SPILL(</t>
+  </si>
+  <si>
+    <t>SPILL()</t>
   </si>
   <si>
     <t>C2</t>
@@ -1074,24 +1107,6 @@
     <t>X plus MATCH.</t>
   </si>
   <si>
-    <t>=XMATCH</t>
-  </si>
-  <si>
-    <t>=XMATCH(</t>
-  </si>
-  <si>
-    <t>=XMATCH()</t>
-  </si>
-  <si>
-    <t>XMATCH</t>
-  </si>
-  <si>
-    <t>XMATCH(</t>
-  </si>
-  <si>
-    <t>XMATCH()</t>
-  </si>
-  <si>
     <t>Which modern function returns a position with an exact match by default?  (from F4-4 Power Couple)</t>
   </si>
   <si>
@@ -2434,7 +2449,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ DYNAMIC ARRAYS</t>
@@ -3208,7 +3223,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3218,12 +3233,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3233,32 +3248,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3268,30 +3283,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F7-1 Spill Zone'!$G$14:$G$41)&amp;" / 210"</f>
@@ -3306,15 +3321,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F7-2 Sifter'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3329,15 +3344,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F7-3 Sorter'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3352,15 +3367,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F7-4 Combo'!$G$12:$G$36)&amp;" / 180"</f>
@@ -3375,15 +3390,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM(Boss!$G$14:$G$35)&amp;" / 180"</f>
@@ -3398,12 +3413,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">(SUM('F7-1 Spill Zone'!$G$14:$G$41)+SUM('F7-2 Sifter'!$G$13:$G$38)+SUM('F7-3 Sorter'!$G$13:$G$39)+SUM('F7-4 Combo'!$G$12:$G$36)+SUM(Boss!$G$14:$G$35))&amp;" / 960"</f>
@@ -3412,19 +3427,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">_xlfn.LET(_xlpm.p,(SUM('F7-1 Spill Zone'!$G$14:$G$41)+SUM('F7-2 Sifter'!$G$13:$G$38)+SUM('F7-3 Sorter'!$G$13:$G$39)+SUM('F7-4 Combo'!$G$12:$G$36)+SUM(Boss!$G$14:$G$35))/960,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3433,16 +3448,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
-        <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Start!$E$17="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>F7-1 Spill Zone</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -3479,7 +3494,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3490,7 +3505,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3509,7 +3524,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3520,19 +3535,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C8" s="31" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -3541,7 +3556,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C9" s="31">
         <v>15</v>
@@ -3549,7 +3564,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F7-1 Spill Zone'!$G$14:$G$41)&gt;=210*0.5,SUM('F7-2 Sifter'!$G$13:$G$38)&gt;=190*0.5,SUM('F7-3 Sorter'!$G$13:$G$39)&gt;=200*0.5,SUM('F7-4 Combo'!$G$12:$G$36)&gt;=180*0.5),"OPEN","LOCKED")</f>
@@ -3562,7 +3577,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3596,7 +3611,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B14" s="32" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function lets you name a value inside a formula?  (from F7-4 Combo)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3619,7 +3634,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B15" s="32" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","In =SORT"&amp;"(UNIQUE"&amp;"(E6:E25)), which function removes the duplicates?  (from F7-4 Combo)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3627,7 +3642,7 @@
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
-        <f t="array" ref="D15">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$E$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D15">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$15,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$J$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E15" s="22"/>
@@ -3642,7 +3657,7 @@
     </row>
     <row r="16" spans="1:7" ht="51.25" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B16" s="32" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","What is it called when one formula's results flow into neighboring cells?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3665,7 +3680,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B17" s="32" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which error appears when a spill range is blocked?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3673,7 +3688,7 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
-        <f t="array" ref="D17">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$17,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$83:$G$83),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D17">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$17,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$83:$L$83),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E17" s="22"/>
@@ -3688,7 +3703,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B18" s="32" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","How do you refer to the whole spill that starts in H5?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3711,7 +3726,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B19" s="32" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which function spills a list of sequential numbers?  (from F7-1 Spill Zone)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3734,7 +3749,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which function returns only the rows that meet a condition?  (from F7-2 Sifter)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3757,7 +3772,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","In FILTER, which operator joins two conditions so BOTH must be true?  (from F7-2 Sifter)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3780,7 +3795,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3791,7 +3806,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3819,14 +3834,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In K6 spill the numbers 1 to 5.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$K$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2801)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$K$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2801)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$K$6)=_xlfn.ANCHORARRAY(Key!$E$2801)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2801))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2801))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SEQUENCE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SEQUENCE"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3844,14 +3859,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In M6 spill the West orders, every column.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$M$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2901)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$M$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2901)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$M$6)=_xlfn.ANCHORARRAY(Key!$E$2901)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2901))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2901))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3869,14 +3884,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In K14 spill the Order IDs of Kim's orders with more than 20 units.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$K$14),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$K$14)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$K$14),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$K$14),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$K$14))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3001)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$K$14))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3001)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$K$14)=_xlfn.ANCHORARRAY(Key!$E$3001)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3001))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3001))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$14)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3894,17 +3909,17 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In K30 spill the Units column sorted largest first.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
-        <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$K$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$K$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$K$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$K$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$K$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3101)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$K$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3101)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$K$30)=_xlfn.ANCHORARRAY(Key!$E$3101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$30)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT"),"✘ TRY AGAIN")))),"LOCKED")</f>
+        <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$K$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$K$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$K$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$K$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$K$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3101)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$K$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3101)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$K$30)=_xlfn.ANCHORARRAY(Key!$E$3101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3101))),FALSE),IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORTBY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$K$30))))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT/SORTBY"),"✘ TRY AGAIN")))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E29" s="22"/>
@@ -3919,14 +3934,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In M30 spill each Product once.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$M$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3201)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$M$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3201)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$M$30)=_xlfn.ANCHORARRAY(Key!$E$3201)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3201))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3201))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$30)))))),"✔ CLEAR","✘ CLOSE · right result, but use UNIQUE"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -3944,17 +3959,17 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In O30 count the different Products.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
-        <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$O$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$O$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$O$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$O$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$O$30),ABS('Boss Arena'!$O$30-Key!$C$93)&lt;=1E-9*MAX(1,ABS(Key!$C$93))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTA"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$O$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$O$30)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTA and UNIQUE"))))),"LOCKED")</f>
+        <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$O$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$O$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$O$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$O$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$O$30),ABS('Boss Arena'!$O$30-Key!$C$93)&lt;=1E-9*MAX(1,ABS(Key!$C$93))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTA"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$O$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROWS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$O$30)))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$O$30)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTA/ROWS and UNIQUE"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E31" s="22"/>
@@ -3969,17 +3984,17 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In Q30 spill each Rep once, sorted A→Z.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
-        <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$Q$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$Q$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$Q$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$Q$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3301)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3301)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30)=_xlfn.ANCHORARRAY(Key!$E$3301)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3301))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3301))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$Q$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$Q$30)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT and UNIQUE"),"✘ TRY AGAIN")))),"LOCKED")</f>
+        <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$Q$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$Q$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$Q$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$Q$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3301)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3301)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$Q$30)=_xlfn.ANCHORARRAY(Key!$E$3301)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3301))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3301))),FALSE),IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$Q$30))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORTBY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$Q$30)))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$Q$30)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT/SORTBY and UNIQUE"),"✘ TRY AGAIN")))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E32" s="22"/>
@@ -3994,14 +4009,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In U13 add up the whole spill in U6 with U6#.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$U$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$U$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$U$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$U$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$U$13),ABS('Boss Arena'!$U$13-Key!$C$95)&lt;=1E-9*MAX(1,ABS(Key!$C$95))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("#",_xlfn.FORMULATEXT('Boss Arena'!$U$13))),"✔ CLEAR","✘ CLOSE · your formula needs #"))))),"LOCKED")</f>
@@ -4019,14 +4034,14 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B34" s="32" cm="1" t="str">
         <f t="array" ref="B34">IF($C$10="OPEN","In W6 spill the Order IDs sorted by Date, newest first, with SORTBY.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$W$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$W$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$W$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$W$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('Boss Arena'!$W$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3401)),COLUMNS(_xlfn.ANCHORARRAY('Boss Arena'!$W$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3401)),SUM(--(_xlfn.ANCHORARRAY('Boss Arena'!$W$6)=_xlfn.ANCHORARRAY(Key!$E$3401)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$3401))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$3401))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORTBY"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$W$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORTBY"),"✘ TRY AGAIN")))),"LOCKED")</f>
@@ -4044,14 +4059,14 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B35" s="32" cm="1" t="str">
         <f t="array" ref="B35">IF($C$10="OPEN","In W30 filter the Order IDs for the region ""Central"" and show None when nothing matches.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D35" s="21" cm="1" t="str">
         <f t="array" ref="D35">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$W$30),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$W$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$W$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$W$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('Boss Arena'!$W$30),'Boss Arena'!$W$30=Key!$C$97),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$W$30)))))),"✔ CLEAR","✘ CLOSE · right value, but use FILTER"))))),"LOCKED")</f>
@@ -4177,7 +4192,7 @@
   <sheetData>
     <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -4190,10 +4205,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -4219,16 +4234,16 @@
         <v>15</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="U5" s="27" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="W5" s="27" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -4399,7 +4414,7 @@
         <v>1500</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -4425,7 +4440,7 @@
         <v>2250</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="U13" s="29"/>
     </row>
@@ -4708,19 +4723,19 @@
     </row>
     <row r="29" spans="2:23">
       <c r="K29" s="27" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="M29" s="27" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="O29" s="27" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="Q29" s="27" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="W29" s="27" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" spans="2:23">
@@ -4755,7 +4770,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4763,189 +4778,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>61</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>64</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -4957,10 +4972,10 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3401"/>
+  <dimension ref="A1:P3401"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4974,7 +4989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -5000,7 +5015,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -5026,7 +5041,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -5052,7 +5067,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -5078,7 +5093,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -5104,7 +5119,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>122</v>
       </c>
@@ -5130,7 +5145,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>131</v>
       </c>
@@ -5156,7 +5171,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -5182,7 +5197,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -5208,7 +5223,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>161</v>
       </c>
@@ -5216,15 +5231,48 @@
         <v>162</v>
       </c>
       <c r="E11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" t="s">
+        <v>164</v>
+      </c>
+      <c r="J11" t="s">
+        <v>165</v>
+      </c>
+      <c r="K11" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="L11" t="s">
+        <v>157</v>
+      </c>
+      <c r="M11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N11" t="s">
+        <v>166</v>
+      </c>
+      <c r="O11" t="s">
+        <v>167</v>
+      </c>
+      <c r="P11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -5233,44 +5281,44 @@
         <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G12" t="s">
         <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
         <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F13" t="s">
         <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C14" t="s">
         <v>64</v>
@@ -5282,357 +5330,387 @@
         <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C15" t="s">
         <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F15" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G15" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F16" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G16" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E17" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F17" t="s">
         <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>203</v>
+      </c>
+      <c r="H17" t="s">
+        <v>204</v>
+      </c>
+      <c r="I17" t="s">
+        <v>205</v>
+      </c>
+      <c r="J17" t="s">
+        <v>197</v>
+      </c>
+      <c r="K17" t="s">
+        <v>206</v>
+      </c>
+      <c r="L17" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E19" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F19" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G19" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H19" t="s">
         <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="J19" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C22" cm="1">
         <f t="array" ref="C22">SUM(_xlfn.ANCHORARRAY('F7-1 Arena'!$O$6))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F23" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F24" t="s">
         <v>61</v>
       </c>
       <c r="G24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>203</v>
+      </c>
+      <c r="H24" t="s">
+        <v>204</v>
+      </c>
+      <c r="I24" t="s">
+        <v>205</v>
+      </c>
+      <c r="J24" t="s">
+        <v>197</v>
+      </c>
+      <c r="K24" t="s">
+        <v>206</v>
+      </c>
+      <c r="L24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E26" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F26" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G26" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H26" t="s">
         <v>67</v>
       </c>
       <c r="I26" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="J26" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E27" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F27" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E28" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="F28" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G28" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="H28" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E29" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F29" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="G29" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="H29" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="I29" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="J29" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E30" t="s">
-        <v>264</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
-        <v>265</v>
+        <v>164</v>
       </c>
       <c r="G30" t="s">
-        <v>266</v>
+        <v>165</v>
       </c>
       <c r="H30" t="s">
-        <v>267</v>
+        <v>166</v>
       </c>
       <c r="I30" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="J30" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E31" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E32" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F32" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G32" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H32" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C33" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E33" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F33" t="s">
         <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H33" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F34" t="s">
         <v>58</v>
@@ -5646,22 +5724,22 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" t="s">
         <v>174</v>
       </c>
-      <c r="F35" t="s">
-        <v>168</v>
-      </c>
       <c r="G35" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
         <v>64</v>
@@ -5669,86 +5747,86 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E36" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F36" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="G36" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H36" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J36" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E37" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F37" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E38" t="s">
         <v>62</v>
       </c>
       <c r="F38" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G38" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H38" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C41" cm="1" t="str">
         <f t="array" ref="C41">_xlfn._xlws.FILTER('F7-2 Arena'!$B$6:$B$25,'F7-2 Arena'!$D$6:$D$25="Central","None")</f>
@@ -5757,264 +5835,264 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E42" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F42" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="G42" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H42" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I42" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J42" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E43" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F43" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E44" t="s">
         <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H44" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E45" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F45" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="G45" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="H45" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I45" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J45" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E46" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F46" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G46" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="H46" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="I46" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J46" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E47" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F47" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="G47" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="H47" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="I47" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="J47" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B48" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E48" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F48" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="G48" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H48" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I48" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J48" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E49" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F49" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="G49" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H49" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I49" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J49" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E50" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F50" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="G50" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H50" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I50" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J50" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E51" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F51" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G51" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H51" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="I51" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J51" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B52" t="s">
         <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E52" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F52" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G52" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H52" t="s">
         <v>67</v>
@@ -6022,158 +6100,158 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E53" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F53" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G53" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H53" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B54" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C54" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E54" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F54" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="G54" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H54" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s">
         <v>95</v>
       </c>
       <c r="E55" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F55" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="G55" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="H55" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I55" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J55" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E56" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F56" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="G56" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H56" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I56" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J56" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E57" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F57" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G57" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H57" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I57" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J57" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B61" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C61" cm="1">
         <f t="array" ref="C61">COUNTA(_xlfn.UNIQUE('F7-3 Arena'!$E$6:$E$25))</f>
@@ -6182,284 +6260,284 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s">
         <v>95</v>
       </c>
       <c r="E62" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F62" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="G62" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="H62" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I62" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="J62" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E63" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F63" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="G63" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H63" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I63" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J63" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B64" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E64" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F64" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G64" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H64" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I64" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J64" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E65" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F65" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="G65" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="H65" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="I65" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="J65" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B66" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E66" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F66" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B67" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E67" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F67" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="G67" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="H67" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="I67" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="J67" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E68" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="F68" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="G68" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="H68" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="I68" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="J68" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B69" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E69" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F69" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="G69" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="H69" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="I69" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="J69" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E70" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F70" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="G70" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="H70" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="I70" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="J70" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="E71" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F71" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="G71" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="H71" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="I71" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="J71" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B72" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C72" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E72" t="s">
         <v>67</v>
       </c>
       <c r="F72" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G72" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H72" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C73" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E73" t="s">
         <v>64</v>
@@ -6471,52 +6549,67 @@
         <v>61</v>
       </c>
       <c r="H73" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E74" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F74" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="G74" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H74" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="I74" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="J74" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B75" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E75" t="s">
-        <v>185</v>
+        <v>428</v>
+      </c>
+      <c r="F75" t="s">
+        <v>429</v>
+      </c>
+      <c r="G75" t="s">
+        <v>430</v>
+      </c>
+      <c r="H75" t="s">
+        <v>191</v>
+      </c>
+      <c r="I75" t="s">
+        <v>431</v>
+      </c>
+      <c r="J75" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B76" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C76" cm="1">
         <f t="array" ref="C76">AVERAGE('F7-4 Arena'!$H$6:$H$25)</f>
@@ -6525,26 +6618,26 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B77" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B78" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B79" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C79" cm="1">
         <f t="array" ref="C79">ROWS(_xlfn.ANCHORARRAY('F7-4 Arena'!$Q$6))</f>
@@ -6553,238 +6646,268 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B80" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E80" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F80" t="s">
+        <v>534</v>
+      </c>
+      <c r="G80" t="s">
+        <v>535</v>
+      </c>
+      <c r="H80" t="s">
+        <v>189</v>
+      </c>
+      <c r="I80" t="s">
+        <v>536</v>
+      </c>
+      <c r="J80" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>576</v>
+      </c>
+      <c r="B81" t="s">
         <v>529</v>
       </c>
-      <c r="G80" t="s">
-        <v>530</v>
-      </c>
-      <c r="H80" t="s">
-        <v>183</v>
-      </c>
-      <c r="I80" t="s">
-        <v>531</v>
-      </c>
-      <c r="J80" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" t="s">
-        <v>571</v>
-      </c>
-      <c r="B81" t="s">
-        <v>524</v>
-      </c>
       <c r="E81" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+        <v>428</v>
+      </c>
+      <c r="F81" t="s">
+        <v>429</v>
+      </c>
+      <c r="G81" t="s">
+        <v>430</v>
+      </c>
+      <c r="H81" t="s">
+        <v>191</v>
+      </c>
+      <c r="I81" t="s">
+        <v>431</v>
+      </c>
+      <c r="J81" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E82" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F82" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G82" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E83" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F83" t="s">
         <v>61</v>
       </c>
       <c r="G83" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
+        <v>203</v>
+      </c>
+      <c r="H83" t="s">
+        <v>204</v>
+      </c>
+      <c r="I83" t="s">
+        <v>205</v>
+      </c>
+      <c r="J83" t="s">
+        <v>197</v>
+      </c>
+      <c r="K83" t="s">
+        <v>206</v>
+      </c>
+      <c r="L83" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E84" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E85" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F85" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G85" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H85" t="s">
         <v>67</v>
       </c>
       <c r="I85" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="J85" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B86" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E86" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F86" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="G86" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H86" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I86" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J86" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E87" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F87" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B88" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B89" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B90" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B91" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B92" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B93" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C93" cm="1">
         <f t="array" ref="C93">COUNTA(_xlfn.UNIQUE('Boss Arena'!$F$6:$F$25))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B94" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B95" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C95" cm="1">
         <f t="array" ref="C95">SUM(_xlfn.ANCHORARRAY('Boss Arena'!$U$6))</f>
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B96" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B97" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C97" cm="1" t="str">
         <f t="array" ref="C97">_xlfn._xlws.FILTER('Boss Arena'!$B$6:$B$25,'Boss Arena'!$D$6:$D$25="Central","None")</f>
@@ -6906,7 +7029,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6917,7 +7040,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7242,14 +7365,14 @@
     </row>
     <row r="23" spans="1:7" ht="35.5" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
-        <f t="array" ref="D23">IFERROR(_xlfn.LET(_xlpm.a,'F7-1 Spill Zone'!$C$23,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$11:$E$11),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D23">IFERROR(_xlfn.LET(_xlpm.a,'F7-1 Spill Zone'!$C$23,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$11:$P$11),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E23" s="22"/>
@@ -7264,7 +7387,7 @@
     </row>
     <row r="25" spans="1:7" ht="22" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -7298,10 +7421,10 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -7320,10 +7443,10 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -7342,10 +7465,10 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -7364,10 +7487,10 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -7386,7 +7509,7 @@
     </row>
     <row r="32" spans="1:7" ht="22" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -7397,7 +7520,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7425,10 +7548,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -7447,14 +7570,14 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
-        <f t="array" ref="D36">IFERROR(_xlfn.LET(_xlpm.a,'F7-1 Spill Zone'!$C$36,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$17:$G$17),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D36">IFERROR(_xlfn.LET(_xlpm.a,'F7-1 Spill Zone'!$C$36,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$17:$L$17),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E36" s="22"/>
@@ -7469,10 +7592,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -7491,10 +7614,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -7513,13 +7636,13 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F7-1 Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('F7-1 Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-1 Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-1 Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-1 Arena'!$K$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2001)),COLUMNS(_xlfn.ANCHORARRAY('F7-1 Arena'!$K$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2001)),SUM(--(_xlfn.ANCHORARRAY('F7-1 Arena'!$K$6)=_xlfn.ANCHORARRAY(Key!$E$2001)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2001))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2001))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SEQUENCE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-1 Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SEQUENCE"),"✘ TRY AGAIN"))))</f>
@@ -7537,13 +7660,13 @@
     </row>
     <row r="40" spans="1:7" ht="51.25" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(IFERROR(AND(_xlfn.ISFORMULA('F7-1 Arena'!$M$6),ROWS(_xlfn.ANCHORARRAY('F7-1 Arena'!$M$6))=5),FALSE),"✔ CLEAR","· not yet")</f>
@@ -7561,13 +7684,13 @@
     </row>
     <row r="41" spans="1:7" ht="35.5" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(ISBLANK('F7-1 Arena'!$K$20),"",IF(NOT(_xlfn.ISFORMULA('F7-1 Arena'!$K$20)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-1 Arena'!$K$20),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-1 Arena'!$K$20),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F7-1 Arena'!$K$20),ABS('F7-1 Arena'!$K$20-Key!$C$22)&lt;=1E-9*MAX(1,ABS(Key!$C$22))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("#",_xlfn.FORMULATEXT('F7-1 Arena'!$K$20))),"✔ CLEAR","✘ CLOSE · your formula needs #")))))</f>
@@ -8266,7 +8389,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8277,7 +8400,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8329,10 +8452,10 @@
         <v>56</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="51.25" customHeight="1">
@@ -8340,10 +8463,10 @@
         <v>59</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="51.25" customHeight="1">
@@ -8351,10 +8474,10 @@
         <v>62</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -8396,7 +8519,7 @@
         <v>82</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -8418,11 +8541,11 @@
         <v>92</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
-        <f t="array" ref="D14">IFERROR(_xlfn.LET(_xlpm.a,'F7-2 Sifter'!$C$14,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$24:$G$24),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D14">IFERROR(_xlfn.LET(_xlpm.a,'F7-2 Sifter'!$C$14,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$24:$L$24),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E14" s="22"/>
@@ -8440,7 +8563,7 @@
         <v>102</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -8462,7 +8585,7 @@
         <v>111</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -8484,7 +8607,7 @@
         <v>120</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -8506,7 +8629,7 @@
         <v>129</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -8528,7 +8651,7 @@
         <v>139</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -8550,7 +8673,7 @@
         <v>149</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -8572,7 +8695,7 @@
         <v>159</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -8591,10 +8714,10 @@
     </row>
     <row r="22" spans="1:7" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -8613,7 +8736,7 @@
     </row>
     <row r="24" spans="1:7" ht="22" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -8647,10 +8770,10 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -8669,10 +8792,10 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -8691,10 +8814,10 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -8713,7 +8836,7 @@
     </row>
     <row r="30" spans="1:7" ht="22" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -8724,7 +8847,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -8752,10 +8875,10 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -8774,10 +8897,10 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -8796,10 +8919,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -8818,13 +8941,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F7-2 Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('F7-2 Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-2 Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-2 Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101)),COLUMNS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101)),SUM(--(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$6)=_xlfn.ANCHORARRAY(Key!$E$2101)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2101))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2101))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-2 Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN"))))</f>
@@ -8842,13 +8965,13 @@
     </row>
     <row r="37" spans="1:7" ht="51.25" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F7-2 Arena'!$K$20),"",IF(NOT(_xlfn.ISFORMULA('F7-2 Arena'!$K$20)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-2 Arena'!$K$20),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-2 Arena'!$K$20),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$20))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2201)),COLUMNS(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$20))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2201)),SUM(--(_xlfn.ANCHORARRAY('F7-2 Arena'!$K$20)=_xlfn.ANCHORARRAY(Key!$E$2201)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2201))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2201))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-2 Arena'!$K$20)))))),"✔ CLEAR","✘ CLOSE · right result, but use FILTER"),"✘ TRY AGAIN"))))</f>
@@ -8866,13 +8989,13 @@
     </row>
     <row r="38" spans="1:7" ht="51.25" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F7-2 Arena'!$K$30),"",IF(NOT(_xlfn.ISFORMULA('F7-2 Arena'!$K$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-2 Arena'!$K$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-2 Arena'!$K$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISTEXT('F7-2 Arena'!$K$30),'F7-2 Arena'!$K$30=Key!$C$41),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-2 Arena'!$K$30)))))),"✔ CLEAR","✘ CLOSE · right value, but use FILTER")))))</f>
@@ -9006,7 +9129,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -9019,10 +9142,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -9048,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -9374,7 +9497,7 @@
         <v>1200</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -9518,7 +9641,7 @@
     </row>
     <row r="29" spans="2:11">
       <c r="K29" s="27" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -9552,7 +9675,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9563,7 +9686,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9615,10 +9738,10 @@
         <v>56</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="67" customHeight="1">
@@ -9626,10 +9749,10 @@
         <v>59</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="51.25" customHeight="1">
@@ -9637,10 +9760,10 @@
         <v>62</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -9682,7 +9805,7 @@
         <v>82</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9704,7 +9827,7 @@
         <v>92</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9726,7 +9849,7 @@
         <v>102</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -9748,7 +9871,7 @@
         <v>111</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9770,7 +9893,7 @@
         <v>120</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9792,7 +9915,7 @@
         <v>129</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9814,7 +9937,7 @@
         <v>139</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9836,7 +9959,7 @@
         <v>149</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9858,7 +9981,7 @@
         <v>159</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9877,10 +10000,10 @@
     </row>
     <row r="22" spans="1:7" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -9899,7 +10022,7 @@
     </row>
     <row r="24" spans="1:7" ht="22" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -9933,10 +10056,10 @@
     </row>
     <row r="26" spans="1:7" ht="19.75" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -9955,10 +10078,10 @@
     </row>
     <row r="27" spans="1:7" ht="19.75" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -9977,10 +10100,10 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -9999,7 +10122,7 @@
     </row>
     <row r="30" spans="1:7" ht="22" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -10010,7 +10133,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -10038,10 +10161,10 @@
     </row>
     <row r="33" spans="1:7" ht="19.75" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -10060,10 +10183,10 @@
     </row>
     <row r="34" spans="1:7" ht="19.75" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -10082,10 +10205,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10104,13 +10227,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F7-3 Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-3 Arena'!$K$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2301)),COLUMNS(_xlfn.ANCHORARRAY('F7-3 Arena'!$K$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2301)),SUM(--(_xlfn.ANCHORARRAY('F7-3 Arena'!$K$6)=_xlfn.ANCHORARRAY(Key!$E$2301)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2301))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2301))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT"),"✘ TRY AGAIN"))))</f>
@@ -10128,13 +10251,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F7-3 Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-3 Arena'!$M$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2401)),COLUMNS(_xlfn.ANCHORARRAY('F7-3 Arena'!$M$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2401)),SUM(--(_xlfn.ANCHORARRAY('F7-3 Arena'!$M$6)=_xlfn.ANCHORARRAY(Key!$E$2401)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2401))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2401))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORTBY"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORTBY"),"✘ TRY AGAIN"))))</f>
@@ -10152,13 +10275,13 @@
     </row>
     <row r="38" spans="1:7" ht="19.75" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F7-3 Arena'!$O$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$O$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$O$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$O$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-3 Arena'!$O$6))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2501)),COLUMNS(_xlfn.ANCHORARRAY('F7-3 Arena'!$O$6))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2501)),SUM(--(_xlfn.ANCHORARRAY('F7-3 Arena'!$O$6)=_xlfn.ANCHORARRAY(Key!$E$2501)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2501))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2501))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$O$6)))))),"✔ CLEAR","✘ CLOSE · right result, but use UNIQUE"),"✘ TRY AGAIN"))))</f>
@@ -10176,13 +10299,13 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F7-3 Arena'!$Q$6),"",IF(NOT(_xlfn.ISFORMULA('F7-3 Arena'!$Q$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-3 Arena'!$Q$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-3 Arena'!$Q$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F7-3 Arena'!$Q$6),ABS('F7-3 Arena'!$Q$6-Key!$C$61)&lt;=1E-9*MAX(1,ABS(Key!$C$61))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTA"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$Q$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-3 Arena'!$Q$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTA and UNIQUE")))))</f>
@@ -10320,7 +10443,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -10333,10 +10456,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -10362,16 +10485,16 @@
         <v>15</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="O5" s="27" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -10866,7 +10989,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10877,7 +11000,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10929,10 +11052,10 @@
         <v>56</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="67" customHeight="1">
@@ -10940,10 +11063,10 @@
         <v>59</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="22" customHeight="1">
@@ -10985,7 +11108,7 @@
         <v>82</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" cm="1" t="str">
@@ -11007,7 +11130,7 @@
         <v>92</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -11029,7 +11152,7 @@
         <v>102</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -11051,7 +11174,7 @@
         <v>111</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -11073,7 +11196,7 @@
         <v>120</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -11095,7 +11218,7 @@
         <v>129</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -11117,7 +11240,7 @@
         <v>139</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -11139,7 +11262,7 @@
         <v>149</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -11161,7 +11284,7 @@
         <v>159</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -11180,10 +11303,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -11202,7 +11325,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -11236,10 +11359,10 @@
     </row>
     <row r="25" spans="1:7" ht="35.5" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -11258,10 +11381,10 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -11280,7 +11403,7 @@
     </row>
     <row r="28" spans="1:7" ht="22" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -11291,7 +11414,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="11" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -11319,10 +11442,10 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -11341,14 +11464,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
-        <f t="array" ref="D32">IFERROR(_xlfn.LET(_xlpm.a,'F7-4 Combo'!$C$32,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$75:$E$75),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D32">IFERROR(_xlfn.LET(_xlpm.a,'F7-4 Combo'!$C$32,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$75:$J$75),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E32" s="22"/>
@@ -11363,13 +11486,13 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F7-4 Arena'!$K$6),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F7-4 Arena'!$K$6),ABS('F7-4 Arena'!$K$6-Key!$C$76)&lt;=1E-9*MAX(1,ABS(Key!$C$76))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"LET"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use LET")))))</f>
@@ -11387,13 +11510,13 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(ISBLANK('F7-4 Arena'!$K$10),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$10))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2601)),COLUMNS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$10))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2601)),SUM(--(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$10)=_xlfn.ANCHORARRAY(Key!$E$2601)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2601))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2601))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$10))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$10)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT and UNIQUE"),"✘ TRY AGAIN"))))</f>
@@ -11411,13 +11534,13 @@
     </row>
     <row r="35" spans="1:7" ht="51.25" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D35" s="21" cm="1" t="str">
         <f t="array" ref="D35">IF(ISBLANK('F7-4 Arena'!$K$20),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$20)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$20),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$20),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(IFERROR(AND(ROWS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$20))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2701)),COLUMNS(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$20))=COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2701)),SUM(--(_xlfn.ANCHORARRAY('F7-4 Arena'!$K$20)=_xlfn.ANCHORARRAY(Key!$E$2701)))=ROWS(_xlfn.ANCHORARRAY(Key!$E$2701))*COLUMNS(_xlfn.ANCHORARRAY(Key!$E$2701))),FALSE),IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SORT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$20))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"UNIQUE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$20))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"FILTER"&amp;"(",UPPER(_xlfn.FORMULATEXT('F7-4 Arena'!$K$20)))))),"✔ CLEAR","✘ CLOSE · right result, but use SORT and UNIQUE and FILTER"),"✘ TRY AGAIN"))))</f>
@@ -11435,13 +11558,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F7-4 Arena'!$K$30),"",IF(NOT(_xlfn.ISFORMULA('F7-4 Arena'!$K$30)),"✘ That's a typed value · enter a formula",IF(ISERROR('F7-4 Arena'!$K$30),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F7-4 Arena'!$K$30),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F7-4 Arena'!$K$30),ABS('F7-4 Arena'!$K$30-Key!$C$79)&lt;=1E-9*MAX(1,ABS(Key!$C$79))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("#",_xlfn.FORMULATEXT('F7-4 Arena'!$K$30))),"✔ CLEAR","✘ CLOSE · your formula needs #")))))</f>
@@ -11569,7 +11692,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -11582,10 +11705,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -11611,10 +11734,10 @@
         <v>15</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -11714,7 +11837,7 @@
         <v>1000</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -11948,7 +12071,7 @@
         <v>1200</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -12092,7 +12215,7 @@
     </row>
     <row r="29" spans="2:11">
       <c r="K29" s="27" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" spans="2:11">
